--- a/artfynd/A 15075-2022 artfynd.xlsx
+++ b/artfynd/A 15075-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15075-2022 artfynd.xlsx
+++ b/artfynd/A 15075-2022 artfynd.xlsx
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121142766</v>
+        <v>121142769</v>
       </c>
       <c r="B8" t="n">
-        <v>90707</v>
+        <v>100347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,34 +1356,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495612</v>
+        <v>495584</v>
       </c>
       <c r="R8" t="n">
-        <v>6542744</v>
+        <v>6542581</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1687,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121142769</v>
+        <v>121142766</v>
       </c>
       <c r="B11" t="n">
-        <v>100337</v>
+        <v>90717</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,35 +1700,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495584</v>
+        <v>495612</v>
       </c>
       <c r="R11" t="n">
-        <v>6542581</v>
+        <v>6542744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 15075-2022 artfynd.xlsx
+++ b/artfynd/A 15075-2022 artfynd.xlsx
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121142769</v>
+        <v>121142771</v>
       </c>
       <c r="B8" t="n">
-        <v>100347</v>
+        <v>8421</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,31 +1360,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495584</v>
+        <v>495553</v>
       </c>
       <c r="R8" t="n">
-        <v>6542581</v>
+        <v>6542607</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,12 +1431,18 @@
           <t>2023-10-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1454,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142771</v>
+        <v>121142768</v>
       </c>
       <c r="B9" t="n">
-        <v>8421</v>
+        <v>8432</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1477,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495553</v>
+        <v>495583</v>
       </c>
       <c r="R9" t="n">
-        <v>6542607</v>
+        <v>6542661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121142768</v>
+        <v>121142766</v>
       </c>
       <c r="B10" t="n">
-        <v>8432</v>
+        <v>90729</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,36 +1590,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1620,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495583</v>
+        <v>495612</v>
       </c>
       <c r="R10" t="n">
-        <v>6542661</v>
+        <v>6542744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,18 +1663,12 @@
           <t>2023-10-26</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1688,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121142766</v>
+        <v>121142769</v>
       </c>
       <c r="B11" t="n">
-        <v>90717</v>
+        <v>100360</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,34 +1699,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495612</v>
+        <v>495584</v>
       </c>
       <c r="R11" t="n">
-        <v>6542744</v>
+        <v>6542581</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 15075-2022 artfynd.xlsx
+++ b/artfynd/A 15075-2022 artfynd.xlsx
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121142771</v>
+        <v>121142768</v>
       </c>
       <c r="B8" t="n">
-        <v>8421</v>
+        <v>8432</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,21 +1360,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495553</v>
+        <v>495583</v>
       </c>
       <c r="R8" t="n">
-        <v>6542607</v>
+        <v>6542661</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142768</v>
+        <v>121142766</v>
       </c>
       <c r="B9" t="n">
-        <v>8432</v>
+        <v>90730</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,36 +1473,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1510,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495583</v>
+        <v>495612</v>
       </c>
       <c r="R9" t="n">
-        <v>6542661</v>
+        <v>6542744</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,18 +1546,12 @@
           <t>2023-10-26</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1578,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121142766</v>
+        <v>121142769</v>
       </c>
       <c r="B10" t="n">
-        <v>90729</v>
+        <v>100361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,34 +1582,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1625,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495612</v>
+        <v>495584</v>
       </c>
       <c r="R10" t="n">
-        <v>6542744</v>
+        <v>6542581</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121142769</v>
+        <v>121142771</v>
       </c>
       <c r="B11" t="n">
-        <v>100360</v>
+        <v>8421</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,31 +1696,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1735,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495584</v>
+        <v>495553</v>
       </c>
       <c r="R11" t="n">
-        <v>6542581</v>
+        <v>6542607</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,12 +1767,18 @@
           <t>2023-10-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15075-2022 artfynd.xlsx
+++ b/artfynd/A 15075-2022 artfynd.xlsx
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121142768</v>
+        <v>121142766</v>
       </c>
       <c r="B8" t="n">
-        <v>8432</v>
+        <v>90733</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,36 +1356,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495583</v>
+        <v>495612</v>
       </c>
       <c r="R8" t="n">
-        <v>6542661</v>
+        <v>6542744</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,18 +1429,12 @@
           <t>2023-10-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1461,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142766</v>
+        <v>121142771</v>
       </c>
       <c r="B9" t="n">
-        <v>90730</v>
+        <v>8424</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,34 +1465,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495612</v>
+        <v>495553</v>
       </c>
       <c r="R9" t="n">
-        <v>6542744</v>
+        <v>6542607</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,12 +1540,18 @@
           <t>2023-10-26</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>121142769</v>
       </c>
       <c r="B10" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121142771</v>
+        <v>121142768</v>
       </c>
       <c r="B11" t="n">
-        <v>8421</v>
+        <v>8435</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495553</v>
+        <v>495583</v>
       </c>
       <c r="R11" t="n">
-        <v>6542607</v>
+        <v>6542661</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 15075-2022 artfynd.xlsx
+++ b/artfynd/A 15075-2022 artfynd.xlsx
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142771</v>
+        <v>121142768</v>
       </c>
       <c r="B9" t="n">
-        <v>8424</v>
+        <v>8435</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,21 +1469,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495553</v>
+        <v>495583</v>
       </c>
       <c r="R9" t="n">
-        <v>6542607</v>
+        <v>6542661</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121142769</v>
+        <v>121142771</v>
       </c>
       <c r="B10" t="n">
-        <v>100364</v>
+        <v>8424</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,31 +1586,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1618,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495584</v>
+        <v>495553</v>
       </c>
       <c r="R10" t="n">
-        <v>6542581</v>
+        <v>6542607</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,12 +1657,18 @@
           <t>2023-10-26</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1680,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121142768</v>
+        <v>121142769</v>
       </c>
       <c r="B11" t="n">
-        <v>8435</v>
+        <v>100364</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,32 +1703,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1729,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495583</v>
+        <v>495584</v>
       </c>
       <c r="R11" t="n">
-        <v>6542661</v>
+        <v>6542581</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,18 +1773,12 @@
           <t>2023-10-26</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15075-2022 artfynd.xlsx
+++ b/artfynd/A 15075-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>77819725</v>
+        <v>121142766</v>
       </c>
       <c r="B2" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Odensvi, S om, Nrk</t>
+          <t>Hallsberg-Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495685.1636691905</v>
+        <v>495612</v>
       </c>
       <c r="R2" t="n">
-        <v>6542781.428503767</v>
+        <v>6542744</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-05-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-05-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +763,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Alsumpskog, vid bäck</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112939565</v>
+        <v>121142763</v>
       </c>
       <c r="B3" t="n">
-        <v>56901</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +790,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,17 +818,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Odensvi skans, Nrk</t>
+          <t>Hallsberg-Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495575</v>
+        <v>495594</v>
       </c>
       <c r="R3" t="n">
-        <v>6542719</v>
+        <v>6542855</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,47 +884,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112939387</v>
+        <v>112939565</v>
       </c>
       <c r="B4" t="n">
-        <v>96352</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220250</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495480</v>
+        <v>495575</v>
       </c>
       <c r="R4" t="n">
-        <v>6542699</v>
+        <v>6542719</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -994,7 +971,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1013,15 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112939323</v>
+        <v>112939563</v>
       </c>
       <c r="B5" t="n">
-        <v>96352</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,27 +1000,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220250</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495649</v>
+        <v>495575</v>
       </c>
       <c r="R5" t="n">
-        <v>6542852</v>
+        <v>6542719</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1120,15 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112939563</v>
+        <v>121142765</v>
       </c>
       <c r="B6" t="n">
-        <v>8428</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,17 +1136,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Odensvi skans, Nrk</t>
+          <t>Hallsberg-Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495575</v>
+        <v>495609</v>
       </c>
       <c r="R6" t="n">
-        <v>6542719</v>
+        <v>6542783</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,6 +1176,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,15 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112939568</v>
+        <v>121142768</v>
       </c>
       <c r="B7" t="n">
-        <v>8418</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,23 +1242,23 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Odensvi skans, Nrk</t>
+          <t>Hallsberg-Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495532</v>
+        <v>495583</v>
       </c>
       <c r="R7" t="n">
-        <v>6542643</v>
+        <v>6542661</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,6 +1288,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,60 +1320,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121142766</v>
+        <v>112939568</v>
       </c>
       <c r="B8" t="n">
-        <v>90733</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Nrk</t>
+          <t>Odensvi skans, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495612</v>
+        <v>495532</v>
       </c>
       <c r="R8" t="n">
-        <v>6542744</v>
+        <v>6542642</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,6 +1408,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1453,15 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121142768</v>
+        <v>113246952</v>
       </c>
       <c r="B9" t="n">
-        <v>8435</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,14 +1467,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Nrk</t>
+          <t>Odensvi skans, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495583</v>
+        <v>495642</v>
       </c>
       <c r="R9" t="n">
-        <v>6542661</v>
+        <v>6542627</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,17 +1501,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,12 +1537,7 @@
         <v>121142771</v>
       </c>
       <c r="B10" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,58 +1646,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121142769</v>
+        <v>77819722</v>
       </c>
       <c r="B11" t="n">
-        <v>100364</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>220075</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Nrk</t>
+          <t>Odensvi, S om, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495584</v>
+        <v>495665</v>
       </c>
       <c r="R11" t="n">
-        <v>6542581</v>
+        <v>6542821</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,12 +1716,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2019-05-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2019-05-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,19 +1732,864 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Alsumpskog, vid bäck</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>77819723</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Odensvi, S om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>495675</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6542801</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2019-05-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2019-05-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Alsumpskog, vid bäck</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>77819724</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Odensvi, S om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>495685</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6542781</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2019-05-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2019-05-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Alsumpskog, vid bäck</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>77819725</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Odensvi, S om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>495685</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6542781</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2019-05-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2019-05-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Alsumpskog, vid bäck</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112939323</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Odensvi skans, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>495649</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6542851</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>112939387</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Odensvi skans, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>495480</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6542699</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121142762</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>495512</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6542601</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113247007</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Odensvi skans, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>495607</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6542564</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121142769</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>495584</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6542581</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
